--- a/accton/dist/20261025_智邦模型_v0.1.xlsx
+++ b/accton/dist/20261025_智邦模型_v0.1.xlsx
@@ -4263,7 +4263,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4282,7 +4282,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4481,7 +4481,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4500,7 +4500,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4602,7 +4602,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4621,7 +4621,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4723,7 +4723,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4742,7 +4742,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4844,7 +4844,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4863,7 +4863,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4965,7 +4965,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4984,7 +4984,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/accton/dist/20261025_智邦模型_v0.1.xlsx
+++ b/accton/dist/20261025_智邦模型_v0.1.xlsx
@@ -4282,7 +4282,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4500,7 +4500,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4621,7 +4621,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4742,7 +4742,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4863,7 +4863,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4984,7 +4984,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
